--- a/worked_examples/AIHE-CASE12_model_update_incident_response_and_renewal_decision/workbook/xlsx/AIHE-CASE12_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE12_model_update_incident_response_and_renewal_decision/workbook/xlsx/AIHE-CASE12_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R5f7a15f98998485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R303c8daf8367445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Red9f4c52ae224199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R9bfa4f8b15e4470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R863844b3b3f545a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R622ecf3a669248b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R168b135115e944dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R49dd5b351f184a65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="38">
     <x:border/>
@@ -397,7 +413,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="128">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,7 +422,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -414,7 +430,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -431,22 +447,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -463,22 +479,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -523,22 +539,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -553,22 +569,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -623,20 +639,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -659,6 +675,59 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -711,9 +780,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -822,25 +891,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Model Update, Incident Response, and Renewal Decision</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -848,7 +917,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="114" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -856,7 +925,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="114" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -864,7 +933,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="114" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -872,7 +941,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="114" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -880,7 +949,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="114" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -888,7 +957,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="114" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -896,7 +965,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="114" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -904,7 +973,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="116" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -933,38 +1002,38 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
+      <x:c r="G1" s="110"/>
+      <x:c r="H1" s="110"/>
+      <x:c r="I1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>Version 2.3.1</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Version 2.4.0</x:v>
       </x:c>
-      <x:c r="D3" s="59" t="str">
+      <x:c r="D3" s="123" t="str">
         <x:v>Threshold</x:v>
       </x:c>
-      <x:c r="E3" s="91" t="str">
+      <x:c r="E3" s="124" t="str">
         <x:v>Threshold breach</x:v>
       </x:c>
-      <x:c r="G3" s="57" t="str">
+      <x:c r="G3" s="121" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="H3" s="59" t="str">
+      <x:c r="H3" s="123" t="str">
         <x:v>Formula result</x:v>
       </x:c>
     </x:row>
@@ -1107,24 +1176,24 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>Version 2.3.1</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Version 2.4.0</x:v>
       </x:c>
-      <x:c r="D3" s="59" t="str">
+      <x:c r="D3" s="123" t="str">
         <x:v>Threshold</x:v>
       </x:c>
     </x:row>
@@ -1209,28 +1278,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Model Update, Incident Response, and Renewal Decision</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="121" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="123" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1251,66 +1320,66 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="97" t="str">
+      <x:c r="A8" s="125" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B8" s="97"/>
-      <x:c r="C8" s="97"/>
-      <x:c r="D8" s="97"/>
-      <x:c r="E8" s="97"/>
-      <x:c r="F8" s="97"/>
+      <x:c r="B8" s="125"/>
+      <x:c r="C8" s="125"/>
+      <x:c r="D8" s="125"/>
+      <x:c r="E8" s="125"/>
+      <x:c r="F8" s="125"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="102" t="str">
+      <x:c r="A9" s="126" t="str">
         <x:v>Version 2.4.0 breaches false-positive, alert-volume, response-time, and near-miss thresholds. Use should be restricted immediately, evidence preserved, and rollback to 2.3.1 performed where safe. Restart should depend on local testing of the model, interface, threshold, and workflow under realistic capacity. Renewal should require improved update notice, audit access, rollback support, and effectiveness evidence.</x:v>
       </x:c>
-      <x:c r="B9" s="102"/>
-      <x:c r="C9" s="102"/>
-      <x:c r="D9" s="102"/>
-      <x:c r="E9" s="102"/>
-      <x:c r="F9" s="102"/>
+      <x:c r="B9" s="126"/>
+      <x:c r="C9" s="126"/>
+      <x:c r="D9" s="126"/>
+      <x:c r="E9" s="126"/>
+      <x:c r="F9" s="126"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="102"/>
-      <x:c r="B10" s="102"/>
-      <x:c r="C10" s="102"/>
-      <x:c r="D10" s="102"/>
-      <x:c r="E10" s="102"/>
-      <x:c r="F10" s="102"/>
+      <x:c r="A10" s="126"/>
+      <x:c r="B10" s="126"/>
+      <x:c r="C10" s="126"/>
+      <x:c r="D10" s="126"/>
+      <x:c r="E10" s="126"/>
+      <x:c r="F10" s="126"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="102"/>
-      <x:c r="B11" s="102"/>
-      <x:c r="C11" s="102"/>
-      <x:c r="D11" s="102"/>
-      <x:c r="E11" s="102"/>
-      <x:c r="F11" s="102"/>
+      <x:c r="A11" s="126"/>
+      <x:c r="B11" s="126"/>
+      <x:c r="C11" s="126"/>
+      <x:c r="D11" s="126"/>
+      <x:c r="E11" s="126"/>
+      <x:c r="F11" s="126"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="102"/>
-      <x:c r="B12" s="102"/>
-      <x:c r="C12" s="102"/>
-      <x:c r="D12" s="102"/>
-      <x:c r="E12" s="102"/>
-      <x:c r="F12" s="102"/>
+      <x:c r="A12" s="126"/>
+      <x:c r="B12" s="126"/>
+      <x:c r="C12" s="126"/>
+      <x:c r="D12" s="126"/>
+      <x:c r="E12" s="126"/>
+      <x:c r="F12" s="126"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="102"/>
-      <x:c r="B13" s="102"/>
-      <x:c r="C13" s="102"/>
-      <x:c r="D13" s="102"/>
-      <x:c r="E13" s="102"/>
-      <x:c r="F13" s="102"/>
+      <x:c r="A13" s="126"/>
+      <x:c r="B13" s="126"/>
+      <x:c r="C13" s="126"/>
+      <x:c r="D13" s="126"/>
+      <x:c r="E13" s="126"/>
+      <x:c r="F13" s="126"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="108" t="str">
+      <x:c r="A15" s="127" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B15" s="108"/>
-      <x:c r="C15" s="108"/>
-      <x:c r="D15" s="108"/>
-      <x:c r="E15" s="108"/>
-      <x:c r="F15" s="108"/>
+      <x:c r="B15" s="127"/>
+      <x:c r="C15" s="127"/>
+      <x:c r="D15" s="127"/>
+      <x:c r="E15" s="127"/>
+      <x:c r="F15" s="127"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
